--- a/Results and Summary/Summary Table (PCA vs Full).xlsx
+++ b/Results and Summary/Summary Table (PCA vs Full).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83d3d0baac882484/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afolabi Soetan\Downloads\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A88E2899-A4AB-4CB1-8155-99F4F35E22B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F30ADCD-9D7F-40B2-8485-EEC950A807B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{48A8BC7E-A115-438E-A58D-AD33FE7420C8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
   <si>
     <t>Model</t>
   </si>
@@ -96,6 +96,24 @@
   </si>
   <si>
     <t>See E8</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>See E10</t>
+  </si>
+  <si>
+    <t>See D10</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>See D12</t>
+  </si>
+  <si>
+    <t>See E12</t>
   </si>
 </sst>
 </file>
@@ -475,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4673BA-7B51-4C3B-9C10-A94940BB5E9F}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -639,21 +657,80 @@
         <v>19</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D10">
+        <v>0.503</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.78649999999999998</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="D12">
+        <v>0.224</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.81845000000000001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090126F964B472F42BF44093AB6677E87" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e278873dc1fca5aa5836c9b4a4f7c188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="09d467f3-b700-42ea-8d14-5b9cd132b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a263b2194a8338e0b3025a38ae8e56f9" ns3:_="">
     <xsd:import namespace="09d467f3-b700-42ea-8d14-5b9cd132b1f3"/>
@@ -803,6 +880,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -812,14 +898,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71F705D9-D2DE-4111-9A5D-CE379C9B5428}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{892C33AB-4D3F-483D-ADB1-B38170E01A1B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -837,18 +915,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71F705D9-D2DE-4111-9A5D-CE379C9B5428}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{771EA204-CF3F-4896-A8D8-AC3C1E2B2578}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="09d467f3-b700-42ea-8d14-5b9cd132b1f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="09d467f3-b700-42ea-8d14-5b9cd132b1f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
